--- a/Excel/LogicalFunctions.xlsx
+++ b/Excel/LogicalFunctions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25D9D41-19F5-4834-B87D-7ED0BBE6264F}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C51F4D-D5BB-4F40-8238-72174B4C7058}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6530" activeTab="1" xr2:uid="{690719AD-3C35-4EEB-BA93-55ED289BD0BD}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Price</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Q: if score1 greater than 60 and score 2 greater than 50 display Pass else display Fail</t>
+  </si>
+  <si>
+    <t>a</t>
   </si>
 </sst>
 </file>
@@ -703,7 +706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2170455-32A9-495F-914B-4F4759E32DEE}">
-  <dimension ref="C4:G21"/>
+  <dimension ref="C4:G24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.6328125" customWidth="1"/>
@@ -940,6 +943,11 @@
         <v>Fail</v>
       </c>
     </row>
+    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
+      <c r="F24" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Excel/LogicalFunctions.xlsx
+++ b/Excel/LogicalFunctions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C51F4D-D5BB-4F40-8238-72174B4C7058}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D9FC4B4-5CB4-45AB-BA3F-D0DFDF5E55E3}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6530" activeTab="1" xr2:uid="{690719AD-3C35-4EEB-BA93-55ED289BD0BD}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="16">
   <si>
     <t>Price</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>Q: if score1 greater than 60 and score 2 greater than 50 display Pass else display Fail</t>
-  </si>
-  <si>
-    <t>a</t>
   </si>
 </sst>
 </file>
@@ -202,9 +199,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -214,6 +208,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -538,10 +535,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:9" x14ac:dyDescent="0.35">
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="9"/>
     </row>
     <row r="4" spans="3:9" ht="17.5" x14ac:dyDescent="0.45">
       <c r="C4" s="1" t="s">
@@ -555,7 +552,7 @@
       <c r="C5" s="2">
         <v>3000</v>
       </c>
-      <c r="D5" s="5" t="b">
+      <c r="D5" s="4" t="b">
         <f>C5&gt;2000</f>
         <v>1</v>
       </c>
@@ -564,7 +561,7 @@
       <c r="C6" s="2">
         <v>1350</v>
       </c>
-      <c r="D6" s="5" t="b">
+      <c r="D6" s="4" t="b">
         <f t="shared" ref="D6:D11" si="0">C6&gt;2000</f>
         <v>0</v>
       </c>
@@ -573,7 +570,7 @@
       <c r="C7" s="2">
         <v>2001</v>
       </c>
-      <c r="D7" s="5" t="b">
+      <c r="D7" s="4" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -582,7 +579,7 @@
       <c r="C8" s="2">
         <v>100</v>
       </c>
-      <c r="D8" s="5" t="b">
+      <c r="D8" s="4" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -591,7 +588,7 @@
       <c r="C9" s="2">
         <v>4069</v>
       </c>
-      <c r="D9" s="5" t="b">
+      <c r="D9" s="4" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -600,7 +597,7 @@
       <c r="C10" s="2">
         <v>99</v>
       </c>
-      <c r="D10" s="5" t="b">
+      <c r="D10" s="4" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -609,7 +606,7 @@
       <c r="C11" s="2">
         <v>2518</v>
       </c>
-      <c r="D11" s="5" t="b">
+      <c r="D11" s="4" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -618,7 +615,7 @@
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>5000</v>
       </c>
     </row>
@@ -630,14 +627,14 @@
         <f>_xlfn.CONCAT("Greater Than ",$D$13)</f>
         <v>Greater Than 5000</v>
       </c>
-      <c r="I16" s="5"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="3:4" ht="17.5" x14ac:dyDescent="0.45">
       <c r="C17" s="2">
         <v>3000</v>
       </c>
-      <c r="D17" s="5" t="b">
-        <f>C17&gt;$D$13</f>
+      <c r="D17" s="4" t="b">
+        <f t="shared" ref="D17:D23" si="1">C17&gt;$D$13</f>
         <v>0</v>
       </c>
     </row>
@@ -645,8 +642,8 @@
       <c r="C18" s="2">
         <v>1350</v>
       </c>
-      <c r="D18" s="5" t="b">
-        <f>C18&gt;$D$13</f>
+      <c r="D18" s="4" t="b">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -654,8 +651,8 @@
       <c r="C19" s="2">
         <v>2001</v>
       </c>
-      <c r="D19" s="5" t="b">
-        <f>C19&gt;$D$13</f>
+      <c r="D19" s="4" t="b">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -663,8 +660,8 @@
       <c r="C20" s="2">
         <v>100</v>
       </c>
-      <c r="D20" s="5" t="b">
-        <f>C20&gt;$D$13</f>
+      <c r="D20" s="4" t="b">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -672,8 +669,8 @@
       <c r="C21" s="2">
         <v>4069</v>
       </c>
-      <c r="D21" s="5" t="b">
-        <f>C21&gt;$D$13</f>
+      <c r="D21" s="4" t="b">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -681,8 +678,8 @@
       <c r="C22" s="2">
         <v>99</v>
       </c>
-      <c r="D22" s="5" t="b">
-        <f>C22&gt;$D$13</f>
+      <c r="D22" s="4" t="b">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -690,8 +687,8 @@
       <c r="C23" s="2">
         <v>2518</v>
       </c>
-      <c r="D23" s="5" t="b">
-        <f>C23&gt;$D$13</f>
+      <c r="D23" s="4" t="b">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -706,7 +703,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2170455-32A9-495F-914B-4F4759E32DEE}">
-  <dimension ref="C4:G24"/>
+  <dimension ref="C4:G21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="14.6328125" customWidth="1"/>
@@ -725,10 +722,10 @@
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -739,100 +736,100 @@
       </c>
     </row>
     <row r="6" spans="3:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>65</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>98</v>
       </c>
-      <c r="F6" s="5" t="b">
+      <c r="F6" s="4" t="b">
         <f>AND(D6&gt;60,E6&gt;50)</f>
         <v>1</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="3:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>28</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>56</v>
       </c>
-      <c r="F7" s="5" t="b">
+      <c r="F7" s="4" t="b">
         <f t="shared" ref="F7:F11" si="0">AND(D7&gt;60,E7&gt;50)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="3:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>81</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>12</v>
       </c>
-      <c r="F8" s="5" t="b">
+      <c r="F8" s="4" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="3:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>81</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>95</v>
       </c>
-      <c r="F9" s="5" t="b">
+      <c r="F9" s="4" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="3:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>60</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>71</v>
       </c>
-      <c r="F10" s="5" t="b">
+      <c r="F10" s="4" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="3:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>12</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>74</v>
       </c>
-      <c r="F11" s="5" t="b">
+      <c r="F11" s="4" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="14" spans="3:7" x14ac:dyDescent="0.35">
       <c r="C14" t="s">
@@ -843,10 +840,10 @@
       <c r="C15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>6</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -854,98 +851,93 @@
       </c>
     </row>
     <row r="16" spans="3:7" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>65</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>98</v>
       </c>
-      <c r="F16" s="5" t="str">
+      <c r="F16" s="4" t="str">
         <f>IF(AND(D16&gt;60,E16&gt;50),"Pass","Fail")</f>
         <v>Pass</v>
       </c>
     </row>
     <row r="17" spans="3:6" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>28</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>56</v>
       </c>
-      <c r="F17" s="5" t="str">
+      <c r="F17" s="4" t="str">
         <f t="shared" ref="F17:F21" si="1">IF(AND(D17&gt;60,E17&gt;50),"Pass","Fail")</f>
         <v>Fail</v>
       </c>
     </row>
     <row r="18" spans="3:6" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>81</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="8">
         <v>12</v>
       </c>
-      <c r="F18" s="5" t="str">
+      <c r="F18" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fail</v>
       </c>
     </row>
     <row r="19" spans="3:6" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>81</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <v>95</v>
       </c>
-      <c r="F19" s="5" t="str">
+      <c r="F19" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Pass</v>
       </c>
     </row>
     <row r="20" spans="3:6" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>60</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <v>71</v>
       </c>
-      <c r="F20" s="5" t="str">
+      <c r="F20" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fail</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="17.5" x14ac:dyDescent="0.45">
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>12</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <v>74</v>
       </c>
-      <c r="F21" s="5" t="str">
+      <c r="F21" s="4" t="str">
         <f t="shared" si="1"/>
         <v>Fail</v>
-      </c>
-    </row>
-    <row r="24" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="F24" t="s">
-        <v>16</v>
       </c>
     </row>
   </sheetData>
